--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3137,6 +3137,755 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132894822</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>668208</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6691910</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132894832</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>668308</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6691782</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132894824</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>668286</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6691782</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132894825</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>668297</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6691773</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132894833</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>668319</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6691779</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132894826</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>668314</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6691782</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132894823</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>668214</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6691897</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -3674,7 +3674,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132894826</v>
+        <v>132894823</v>
       </c>
       <c r="B31" t="n">
         <v>57142</v>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668314</v>
+        <v>668214</v>
       </c>
       <c r="R31" t="n">
-        <v>6691782</v>
+        <v>6691897</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132894823</v>
+        <v>132894826</v>
       </c>
       <c r="B32" t="n">
         <v>57142</v>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668214</v>
+        <v>668314</v>
       </c>
       <c r="R32" t="n">
-        <v>6691897</v>
+        <v>6691782</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -3674,7 +3674,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132894826</v>
+        <v>132894823</v>
       </c>
       <c r="B31" t="n">
         <v>57145</v>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668314</v>
+        <v>668214</v>
       </c>
       <c r="R31" t="n">
-        <v>6691782</v>
+        <v>6691897</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132894823</v>
+        <v>132894826</v>
       </c>
       <c r="B32" t="n">
         <v>57145</v>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668214</v>
+        <v>668314</v>
       </c>
       <c r="R32" t="n">
-        <v>6691897</v>
+        <v>6691782</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125807856</v>
+        <v>125807858</v>
       </c>
       <c r="B2" t="n">
-        <v>91210</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668270</v>
+        <v>668168</v>
       </c>
       <c r="R2" t="n">
-        <v>6691807</v>
+        <v>6691761</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,48 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125807888</v>
+        <v>128344122</v>
       </c>
       <c r="B3" t="n">
-        <v>4778</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668255</v>
+        <v>668359</v>
       </c>
       <c r="R3" t="n">
-        <v>6691905</v>
+        <v>6691742</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -853,41 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125855910</v>
+        <v>128260561</v>
       </c>
       <c r="B4" t="n">
-        <v>4778</v>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668295</v>
+        <v>667956</v>
       </c>
       <c r="R4" t="n">
-        <v>6691776</v>
+        <v>6691635</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,60 +974,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125855912</v>
+        <v>128260554</v>
       </c>
       <c r="B5" t="n">
-        <v>4778</v>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668276</v>
+        <v>668031</v>
       </c>
       <c r="R5" t="n">
-        <v>6691767</v>
+        <v>6691632</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1046,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1066,68 +1071,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125855888</v>
+        <v>128260556</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668226</v>
+        <v>668353</v>
       </c>
       <c r="R6" t="n">
-        <v>6691879</v>
+        <v>6691720</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1151,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,60 +1168,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125855916</v>
+        <v>128344128</v>
       </c>
       <c r="B7" t="n">
-        <v>98278</v>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668198</v>
+        <v>668138</v>
       </c>
       <c r="R7" t="n">
-        <v>6691900</v>
+        <v>6691627</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1248,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,68 +1265,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125855890</v>
+        <v>127382963</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>93215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>4368</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668217</v>
+        <v>668299</v>
       </c>
       <c r="R8" t="n">
-        <v>6691903</v>
+        <v>6691892</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1353,12 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,22 +1362,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125855913</v>
+        <v>128344126</v>
       </c>
       <c r="B9" t="n">
-        <v>4778</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1396,37 +1385,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668200</v>
+        <v>668368</v>
       </c>
       <c r="R9" t="n">
-        <v>6691772</v>
+        <v>6691735</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1450,12 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1470,60 +1459,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125853668</v>
+        <v>125807856</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668241</v>
+        <v>668270</v>
       </c>
       <c r="R10" t="n">
-        <v>6691789</v>
+        <v>6691807</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1567,60 +1556,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125984242</v>
+        <v>128260536</v>
       </c>
       <c r="B11" t="n">
-        <v>98278</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>667892</v>
+        <v>668066</v>
       </c>
       <c r="R11" t="n">
-        <v>6691648</v>
+        <v>6691644</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1644,12 +1633,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,26 +1649,41 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126056868</v>
+        <v>125853668</v>
       </c>
       <c r="B12" t="n">
-        <v>56849</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1687,42 +1691,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668245</v>
+        <v>668241</v>
       </c>
       <c r="R12" t="n">
-        <v>6691768</v>
+        <v>6691789</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,22 +1765,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127382960</v>
+        <v>128260551</v>
       </c>
       <c r="B13" t="n">
-        <v>4779</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,37 +1788,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668228</v>
+        <v>668206</v>
       </c>
       <c r="R13" t="n">
-        <v>6691916</v>
+        <v>6691675</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1843,12 +1847,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,21 +1868,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1890,48 +1884,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128260536</v>
+        <v>125855888</v>
       </c>
       <c r="B14" t="n">
-        <v>79739</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668066</v>
+        <v>668226</v>
       </c>
       <c r="R14" t="n">
-        <v>6691644</v>
+        <v>6691879</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1955,12 +1957,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,41 +1973,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128260556</v>
+        <v>125855890</v>
       </c>
       <c r="B15" t="n">
-        <v>92806</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2013,37 +2000,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668353</v>
+        <v>668217</v>
       </c>
       <c r="R15" t="n">
-        <v>6691720</v>
+        <v>6691903</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2067,12 +2062,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,22 +2082,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128260554</v>
+        <v>126056868</v>
       </c>
       <c r="B16" t="n">
-        <v>92806</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,37 +2105,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668031</v>
+        <v>668245</v>
       </c>
       <c r="R16" t="n">
-        <v>6691632</v>
+        <v>6691768</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
         <v>128260538</v>
       </c>
       <c r="B17" t="n">
-        <v>56907</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,10 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128260561</v>
+        <v>132894822</v>
       </c>
       <c r="B18" t="n">
-        <v>91277</v>
+        <v>57162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2319,37 +2319,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3215</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>667956</v>
+        <v>668208</v>
       </c>
       <c r="R18" t="n">
-        <v>6691635</v>
+        <v>6691910</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2373,12 +2378,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2405,10 +2415,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128260591</v>
+        <v>132894823</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>57162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2416,46 +2426,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668209</v>
+        <v>668214</v>
       </c>
       <c r="R19" t="n">
-        <v>6691659</v>
+        <v>6691897</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2479,12 +2485,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2493,24 +2504,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2527,53 +2522,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128260551</v>
+        <v>132894824</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>57162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668206</v>
+        <v>668286</v>
       </c>
       <c r="R20" t="n">
-        <v>6691675</v>
+        <v>6691782</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2597,17 +2592,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2634,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128260579</v>
+        <v>132894825</v>
       </c>
       <c r="B21" t="n">
-        <v>4779</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,37 +2640,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668356</v>
+        <v>668297</v>
       </c>
       <c r="R21" t="n">
-        <v>6691715</v>
+        <v>6691773</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2699,12 +2699,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,21 +2720,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2746,48 +2736,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128344122</v>
+        <v>132894826</v>
       </c>
       <c r="B22" t="n">
-        <v>91508</v>
+        <v>57162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668359</v>
+        <v>668314</v>
       </c>
       <c r="R22" t="n">
-        <v>6691742</v>
+        <v>6691782</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2811,17 +2806,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2836,22 +2831,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128344128</v>
+        <v>132894832</v>
       </c>
       <c r="B23" t="n">
-        <v>92810</v>
+        <v>57162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,37 +2854,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668138</v>
+        <v>668308</v>
       </c>
       <c r="R23" t="n">
-        <v>6691627</v>
+        <v>6691782</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2913,12 +2913,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2933,22 +2938,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128344141</v>
+        <v>132894833</v>
       </c>
       <c r="B24" t="n">
-        <v>98553</v>
+        <v>57162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,37 +2961,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668248</v>
+        <v>668319</v>
       </c>
       <c r="R24" t="n">
-        <v>6691654</v>
+        <v>6691779</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3010,12 +3020,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3030,22 +3045,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128344126</v>
+        <v>128260591</v>
       </c>
       <c r="B25" t="n">
-        <v>92443</v>
+        <v>5179</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,37 +3068,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668368</v>
+        <v>668209</v>
       </c>
       <c r="R25" t="n">
-        <v>6691735</v>
+        <v>6691659</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3121,28 +3145,44 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132894822</v>
+        <v>125807887</v>
       </c>
       <c r="B26" t="n">
-        <v>57145</v>
+        <v>4781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,39 +3190,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668208</v>
+        <v>668279</v>
       </c>
       <c r="R26" t="n">
-        <v>6691910</v>
+        <v>6691905</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3209,17 +3244,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3230,6 +3260,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3246,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132894832</v>
+        <v>125807888</v>
       </c>
       <c r="B27" t="n">
-        <v>57145</v>
+        <v>4781</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,39 +3302,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668308</v>
+        <v>668255</v>
       </c>
       <c r="R27" t="n">
-        <v>6691782</v>
+        <v>6691905</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,17 +3356,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,6 +3372,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3353,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132894824</v>
+        <v>125855910</v>
       </c>
       <c r="B28" t="n">
-        <v>57145</v>
+        <v>4781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,42 +3414,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668286</v>
+        <v>668295</v>
       </c>
       <c r="R28" t="n">
-        <v>6691782</v>
+        <v>6691776</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3423,17 +3468,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3448,22 +3488,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132894825</v>
+        <v>125855912</v>
       </c>
       <c r="B29" t="n">
-        <v>57145</v>
+        <v>4781</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3471,42 +3511,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668297</v>
+        <v>668276</v>
       </c>
       <c r="R29" t="n">
-        <v>6691773</v>
+        <v>6691767</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3530,17 +3565,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,22 +3585,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132894833</v>
+        <v>125855913</v>
       </c>
       <c r="B30" t="n">
-        <v>57145</v>
+        <v>4781</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,42 +3608,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668319</v>
+        <v>668200</v>
       </c>
       <c r="R30" t="n">
-        <v>6691779</v>
+        <v>6691772</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3637,17 +3662,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3662,22 +3682,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132894823</v>
+        <v>127382960</v>
       </c>
       <c r="B31" t="n">
-        <v>57145</v>
+        <v>4781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3685,39 +3705,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668214</v>
+        <v>668228</v>
       </c>
       <c r="R31" t="n">
-        <v>6691897</v>
+        <v>6691916</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3744,17 +3759,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3765,6 +3775,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3781,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132894826</v>
+        <v>128260579</v>
       </c>
       <c r="B32" t="n">
-        <v>57145</v>
+        <v>4781</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,42 +3817,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668314</v>
+        <v>668356</v>
       </c>
       <c r="R32" t="n">
-        <v>6691782</v>
+        <v>6691715</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3851,17 +3871,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3872,6 +3887,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3885,6 +3915,588 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125853673</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>668269</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6691918</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Eva-Lena1 Rådberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Eva-Lena1 Rådberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125855915</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>668328</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6691847</v>
+      </c>
+      <c r="S34" t="n">
+        <v>12</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125855916</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>668198</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6691900</v>
+      </c>
+      <c r="S35" t="n">
+        <v>12</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125984242</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>667892</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6691648</v>
+      </c>
+      <c r="S36" t="n">
+        <v>12</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Johanna Sollén Mattsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Johanna Sollén Mattsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128344141</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>668248</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6691654</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125855908</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>668294</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6691884</v>
+      </c>
+      <c r="S38" t="n">
+        <v>12</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19252-2026 artfynd.xlsx
+++ b/artfynd/A 19252-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807858</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260561</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260554</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260556</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344128</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382963</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344126</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807856</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260536</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853668</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260551</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1986,6 +2051,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855888</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855890</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2193,6 +2268,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126056868</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2305,6 +2385,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260538</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2412,6 +2497,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894822</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2519,6 +2609,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894823</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2626,6 +2721,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894824</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2733,6 +2833,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894825</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2840,6 +2945,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894826</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2947,6 +3057,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894832</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3054,6 +3169,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894833</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3176,6 +3296,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260591</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3288,6 +3413,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807887</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3400,6 +3530,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807888</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3497,6 +3632,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855910</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3594,6 +3734,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855912</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3691,6 +3836,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855913</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3803,6 +3953,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382960</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3915,6 +4070,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260579</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4012,6 +4172,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853673</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4109,6 +4274,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855915</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4206,6 +4376,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855916</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4303,6 +4478,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984242</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4400,6 +4580,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344141</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4497,8 +4682,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>